--- a/docs/AT-CREW_서비스기획서_전체_20260728.xlsx
+++ b/docs/AT-CREW_서비스기획서_전체_20260728.xlsx
@@ -263,8 +263,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TblSpec" displayName="TblSpec" ref="A1:J147" headerRowCount="1">
-  <autoFilter ref="A1:J147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TblSpec" displayName="TblSpec" ref="A1:J148" headerRowCount="1">
+  <autoFilter ref="A1:J148"/>
   <tableColumns count="10">
     <tableColumn id="1" name="명세 ID"/>
     <tableColumn id="2" name="화면 ID"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>이메일/Google 방식으로 가입·로그인한다. 가입 시 계정 유형(창작자/기업)을 선택하고, 마지막 단계에서 주 사용 언어(한국어/일본어/중국어/영어)·사용자 이름·약관 동의를 거쳐 계정을 생성한다.</t>
+          <t>이메일/Google 방식으로 가입·로그인한다. 가입 시 계정 유형(창작자/기업)을 선택하고, 마지막 단계에서 주 사용 언어(한국어/일본어/중국어/영어)·사용자 이름·사용자 아이디·약관 동의를 거쳐 계정을 생성한다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>포트폴리오 공유 URL을 발급·복사할 수 있고, 링크를 받은 제3자는 로그인 없이 열람할 수 있다. 경로는 at-crew.com/portfolio/ 로 통일하며, 작가 페이지 포트폴리오는 {사용자 아이디}를, 사용자가 생성한 공유 포트폴리오는 {무작위 고유 ID}를 식별자로 사용한다.</t>
+          <t>포트폴리오 공유 URL을 발급·복사할 수 있고, 링크를 받은 제3자는 로그인 없이 열람할 수 있다. 작가 페이지 포트폴리오는 계정당 1개라 코드 없이 at-crew.com/{사용자 아이디}로, 사용자가 생성한 공유 포트폴리오는 at-crew.com/{사용자 아이디}/portfolio/{6자 코드}(영문 소문자·숫자, 작가 안에서만 유일)로 식별한다. 공유 URL에는 언어 코드를 넣지 않으며, 옛 주소(at-crew.com/portfolio/{사용자 아이디 또는 22자 ID})는 새 주소로 리다이렉트한다.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>계정 정보 표시, 비밀번호 변경(이메일 가입만), 본인 인증(성인 인증), 기업 인증, 마케팅 수신 동의, 성인 콘텐츠 표시, 게시물 언어 선택, 탈퇴를 계정 탭에서 제공하고 요금제 및 결제 탭을 별도 제공한다.</t>
+          <t>계정 정보 표시, 사용자 아이디 변경, 비밀번호 변경(이메일 가입만), 본인 인증(성인 인증), 기업 인증, 마케팅 수신 동의, 성인 콘텐츠 표시, 게시물 언어 선택, 탈퇴를 계정 탭에서 제공하고 요금제 및 결제 탭을 별도 제공한다.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>노션 설정-R04~R14</t>
+          <t>노션 설정-R04~R14·R17</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>계정 유형 선택→가입 방식→주 사용 언어·이름·약관 순</t>
+          <t>계정 유형 선택→가입 방식→주 사용 언어·이름·사용자 아이디·약관 순</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>URL: at-crew.com/art/{고유 ID}</t>
+          <t>URL: at-crew.com/{사용자 아이디}/artwork/{6자 코드}(6자 코드는 영문 소문자·숫자, 작가 안에서만 유일). 옛 주소 at-crew.com/art/{고유 ID}·at-crew.com/artwork/{ID}는 새 주소로 리다이렉트</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>제3자 뷰와 동일 화면 재사용. URL: at-crew.com/creator/{사용자 아이디}</t>
+          <t>제3자 뷰와 동일 화면 재사용. URL: at-crew.com/{사용자 아이디}. 옛 주소 at-crew.com/creator/{사용자 아이디}·at-crew.com/portfolio/{사용자 아이디}는 새 주소로 리다이렉트</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>주 사용 언어 선택·사용자 이름 입력·약관 동의 후 [회원가입 완료하기]</t>
+          <t>주 사용 언어 선택·사용자 이름 입력·사용자 아이디 입력·약관 동의 후 [회원가입 완료하기]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>주 사용 언어 기본값 한국어, 가입 후 변경 불가. 필수 약관 3종 미동의·이름 오류 시 토스트. 이메일 중복은 이 시점 서버 최종 검증</t>
+          <t>주 사용 언어 기본값 한국어, 가입 후 변경 불가. 필수 약관 3종 미동의·이름 오류·사용자 아이디 오류(형식·예약어·중복) 시 토스트. 이메일·사용자 아이디 중복은 이 시점 서버 최종 검증</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>노션 로그인-R19·R07·R02</t>
+          <t>노션 로그인-R19·R07·R02, 설정-R17</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>서버 검증 통과 시 포트폴리오 객체·고유 URL 생성, 상세 화면으로 이동</t>
+          <t>서버 검증 통과 시 포트폴리오 객체·고유 URL(at-crew.com/{사용자 아이디}/portfolio/{6자 코드}) 생성, 상세 화면으로 이동</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>원본과 독립적인 새 고유 ID·URL로 포트폴리오 생성</t>
+          <t>원본과 독립적인 새 6자 코드·URL(at-crew.com/{사용자 아이디}/portfolio/{6자 코드})로 포트폴리오 생성</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>계정 생성 완료 화면(주 사용 언어·이름·약관)</t>
+          <t>계정 생성 완료 화면(주 사용 언어·이름·사용자 아이디·약관)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>주 사용 언어 선택→사용자 이름 입력→약관 동의→[회원가입 완료하기] 순. 완료 시점에 실제 계정 생성 후 설정 페이지 이동+인증 모달.</t>
+          <t>주 사용 언어 선택→사용자 이름 입력→사용자 아이디 입력→약관 동의→[회원가입 완료하기] 순. 완료 시점에 실제 계정 생성 후 설정 페이지 이동+인증 모달.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>주 사용 언어 4개 중 필수 선택(기본값 한국어, 가입 후 변경 불가). 이름 placeholder: 창작자 '활동명, 작가명, 필명 입력'/기업 '기업명, 스튜디오명 입력'. 약관: 전체동의+필수4·선택1</t>
+          <t>주 사용 언어 4개 중 필수 선택(기본값 한국어, 가입 후 변경 불가). 이름 placeholder: 창작자 '활동명, 작가명, 필명 입력'/기업 '기업명, 스튜디오명 입력'. 사용자 아이디 필수 입력: 영문 대소문자·숫자·밑줄(_) 4~14자, 연속 밑줄 불가, 대소문자 무관 중복 불가, 예약어 불가(세부 규칙은 설정-R17, 30일 변경 제한은 가입 시 미적용). 약관: 전체동의+필수4·선택1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>언어 미선택·이름 오류·필수 약관 미동의 시 각각 토스트. 이메일 최종 검증 실패 시 로그인-R06 문구 재사용</t>
+          <t>언어 미선택·이름 오류·사용자 아이디 오류(미입력·형식·예약어·중복)·필수 약관 미동의 시 각각 토스트. 이메일 최종 검증 실패 시 로그인-R06 문구 재사용. 사용자 아이디 형식·예약어·중복 문구는 설정-R17과 동일</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>작성되지 않은 항목은 '-'로 표시. 작가 페이지 URL: at-crew.com/portfolio/{사용자 아이디}(사용자 아이디는 계정별 고유 식별자로 사용자 이름과 별개이며 변경 불가)</t>
+          <t>작성되지 않은 항목은 '-'로 표시. 작가 페이지 URL: at-crew.com/{사용자 아이디}(사용자 아이디는 계정별 고유 식별자로 사용자 이름과 별개이며, 설정 &gt; 계정 탭에서 변경 가능. 변경 규칙은 설정-R17)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>포트폴리오 URL은 at-crew.com/portfolio/ 경로 공통(작가 페이지는 {사용자 아이디}, 공유 포트폴리오는 {고유 ID})</t>
+          <t>포트폴리오 URL: 작가 페이지는 at-crew.com/{사용자 아이디}(계정당 1개라 코드 없음), 공유 포트폴리오는 at-crew.com/{사용자 아이디}/portfolio/{6자 코드}(영문 소문자·숫자, 작가 안에서만 유일)</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>상세 더보기 메뉴 [복제하기] 선택 시 제목 입력·작품 선택 통합 화면으로 진입(생성과 동일 흐름). 제목 입력란에는 '{기존 포트폴리오 이름} 복사본'이 기본값으로 미리 채워진 상태로 노출되며 사용자가 자유롭게 수정할 수 있다(예: 채색 포트폴리오 → 채색 포트폴리오 복사본). 작품은 원본 작품 ID 기준으로 자동 선택된다. [포트폴리오 만들기] 선택 시 유형 선택 모달을 거쳐 원본과 독립적인 새 고유 ID·URL로 생성된다.</t>
+          <t>상세 더보기 메뉴 [복제하기] 선택 시 제목 입력·작품 선택 통합 화면으로 진입(생성과 동일 흐름). 제목 입력란에는 '{기존 포트폴리오 이름} 복사본'이 기본값으로 미리 채워진 상태로 노출되며 사용자가 자유롭게 수정할 수 있다(예: 채색 포트폴리오 → 채색 포트폴리오 복사본). 작품은 원본 작품 ID 기준으로 자동 선택된다. [포트폴리오 만들기] 선택 시 유형 선택 모달을 거쳐 원본과 독립적인 새 6자 코드·URL(at-crew.com/{사용자 아이디}/portfolio/{6자 코드})로 생성된다.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -12935,94 +12935,106 @@
       </c>
       <c r="J143" s="2" t="n"/>
     </row>
-    <row r="144" ht="84" customHeight="1">
+    <row r="144" ht="112" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>설정-R17</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SET-P01</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>사용자 아이디 변경</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>계정 탭에서 새 사용자 아이디를 입력해 변경한다. 변경 즉시 작가 페이지·작품·공유 포트폴리오 주소가 새 사용자 아이디 기준으로 바뀐다. 이전 사용자 아이디는 영구히 다른 계정에 재할당하지 않고, 이전 주소로 접근하면 현재 주소로 연결한다. 탈퇴 계정의 사용자 아이디도 재할당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>영문 대소문자·숫자·밑줄(_) 4~14자, 연속 밑줄 불가, 대소문자 무관 중복 불가, 예약어 불가. 변경 성공 후 30일간 재변경 불가(회원가입 시 입력한 아이디는 30일 제한 산정 대상 아님). 본인이 이전에 쓴 사용자 아이디로는 복귀 가능</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>미입력·현재 아이디와 동일, 4자 미만, 15자 이상, 허용 외 문자, 연속 밑줄, 예약어, 중복, 30일 이내 재변경 등 분기별 토스트</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>새 사용자 아이디를 입력해주세요. / 사용자 아이디는 4자 이상 입력해주세요. / 사용자 아이디는 14자 이하로 입력해주세요. / 사용자 아이디는 영문, 숫자, 밑줄(_)만 사용할 수 있어요. / 밑줄(_)은 연속으로 사용할 수 없어요. / 사용할 수 없는 사용자 아이디예요. 다른 아이디를 입력해주세요. / 이미 사용 중인 사용자 아이디예요. / 사용자 아이디는 YYYY.MM.DD부터 다시 변경할 수 있어요. / 사용자 아이디가 변경되었어요.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>REQ-022</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>노션 설정-R17(2026-10-14) 기준. 회원가입 시 입력 규칙은 로그인-R19</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="84" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
           <t>요금제페이지-R01</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>PLAN-P01</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>요금제 페이지 구성·구매 진입</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>조회·노출</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>비로그인 요금제 페이지. 상품 구분 탭(구독형/단건 게시 상품)+구독형 탭에 결제 주기 토글(월간/연간, 프로 가격에만 적용). 카드: 스타터/프로/단건 2종. 비로그인이 CTA 선택 시 선택 상품 임시 저장 후 로그인·가입 유도, 완료 후 설정&gt;요금제 및 결제 탭으로 이동(가능하면 탭·주기 상태 유지). 로그인 사용자의 CTA도 설정 탭으로 이동.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>스타터 카드는 비로그인 페이지에서만 노출(로그인 후 설정 탭에는 미노출)</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="n"/>
-      <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>REQ-021</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>요금제페이지-R02 내용 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="126" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>요금제-R03</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>PLAN-P01</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>스타터 플랜 카드</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>조회·노출</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>가격 '$0/월·기본 요금제'. CTA [스타터 플랜 시작하기] 선택 시 비로그인은 로그인 페이지로 이동, 로그인·가입 완료 시 스타터 기본 적용.</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>스타터 플랜 카드는 비로그인 요금제 페이지(PLAN-P01)에서만 노출한다. 로그인 후 설정 &gt; 요금제 및 결제 탭에는 스타터 카드를 노출하지 않고 프로 플랜 카드와 단건 게시 상품 카드만 노출한다. 혜택 문구: 작품 최대 4개 업로드/웹 감상에 적합한 화질/기본 작가 페이지/활동 언어 1개(마케팅 문구, 실제 제한값은 마이페이지_작가-R20)</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>REQ-020, REQ-021</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n"/>
-    </row>
-    <row r="146" ht="98" customHeight="1">
+          <t>REQ-021</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>요금제페이지-R02 내용 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="126" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>요금제-R04</t>
+          <t>요금제-R03</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -13032,7 +13044,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>프로 플랜 카드</t>
+          <t>스타터 플랜 카드</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -13042,12 +13054,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>월간 $8.00/월(정가 표기 없음), 연간 $80.00/년(정가 $96.00 취소선+$6.67/월 보조 표기). 연간 카드에 '2개월 무료' Blue 배지. CTA는 이용 상태별 분기: 시작하기/연간 플랜 시작하기/이용 중인 플랜(비활성)/월간·연간 플랜으로 변경하기(Stripe Customer Portal로 이동). 이용 중 카드는 '이용 중인 플랜' 라벨+취소선 미노출.</t>
+          <t>가격 '$0/월·기본 요금제'. CTA [스타터 플랜 시작하기] 선택 시 비로그인은 로그인 페이지로 이동, 로그인·가입 완료 시 스타터 기본 적용.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>혜택: 작품 제한 없이 업로드/선명한 원본 화질/목적별 포트폴리오 생성/여러 활동 언어로 노출 확대. 연간 토글 라벨 옆 '연간 2개월 무료'</t>
+          <t>스타터 플랜 카드는 비로그인 요금제 페이지(PLAN-P01)에서만 노출한다. 로그인 후 설정 &gt; 요금제 및 결제 탭에는 스타터 카드를 노출하지 않고 프로 플랜 카드와 단건 게시 상품 카드만 노출한다. 혜택 문구: 작품 최대 4개 업로드/웹 감상에 적합한 화질/기본 작가 페이지/활동 언어 1개(마케팅 문구, 실제 제한값은 마이페이지_작가-R20)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -13059,10 +13071,10 @@
       </c>
       <c r="J146" s="2" t="n"/>
     </row>
-    <row r="147" ht="56" customHeight="1">
+    <row r="147" ht="98" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>요금제-R05</t>
+          <t>요금제-R04</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -13072,7 +13084,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>단건 게시 상품 카드</t>
+          <t>프로 플랜 카드</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -13082,22 +13094,62 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>팀원 모집글 업로드 $39.99/건(혜택: 1건 등록·지원자 관리·끌어올리기 1회 제공), 끌어올리기 $7.99(혜택: 상단 고정·48시간 노출·팀원 모집글에서 직접 사용), 구인글 업로드 $99.99/건(기업 전용). 전부 표시가가 최종 청구액(별도 세금 안내 없음). CTA [구매하기].</t>
+          <t>월간 $8.00/월(정가 표기 없음), 연간 $80.00/년(정가 $96.00 취소선+$6.67/월 보조 표기). 연간 카드에 '2개월 무료' Blue 배지. CTA는 이용 상태별 분기: 시작하기/연간 플랜 시작하기/이용 중인 플랜(비활성)/월간·연간 플랜으로 변경하기(Stripe Customer Portal로 이동). 이용 중 카드는 '이용 중인 플랜' 라벨+취소선 미노출.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>끌어올리기 카드 하단 안내: 적용 후 48시간 동안 상단 고정 노출 · 마지막 적용 후 48시간 대기 필요</t>
+          <t>혜택: 작품 제한 없이 업로드/선명한 원본 화질/목적별 포트폴리오 생성/여러 활동 언어로 노출 확대. 연간 토글 라벨 옆 '연간 2개월 무료'</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
+          <t>REQ-020, REQ-021</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n"/>
+    </row>
+    <row r="148" ht="56" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>요금제-R05</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>PLAN-P01</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>단건 게시 상품 카드</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>조회·노출</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>팀원 모집글 업로드 $39.99/건(혜택: 1건 등록·지원자 관리·끌어올리기 1회 제공), 끌어올리기 $7.99(혜택: 상단 고정·48시간 노출·팀원 모집글에서 직접 사용), 구인글 업로드 $99.99/건(기업 전용). 전부 표시가가 최종 청구액(별도 세금 안내 없음). CTA [구매하기].</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>끌어올리기 카드 하단 안내: 적용 후 48시간 동안 상단 고정 노출 · 마지막 적용 후 48시간 대기 필요</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
           <t>REQ-021</t>
         </is>
       </c>
-      <c r="J147" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -14026,7 +14078,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>포트폴리오 생성, at-crew.com/portfolio/{고유 ID} URL 발급, 상세 화면 이동</t>
+          <t>포트폴리오 생성, at-crew.com/{사용자 아이디}/portfolio/{6자 코드} URL 발급, 상세 화면 이동</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
